--- a/dist/data/Excel_Maestro.xlsx
+++ b/dist/data/Excel_Maestro.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-5385" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Productos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Categorias">Listas!$A$2:$A$1000</definedName>
@@ -333,8 +333,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H132" headerRowCount="1" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H133" headerRowCount="1" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H133"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Código" dataDxfId="7"/>
     <tableColumn id="2" name="Nombre" dataDxfId="6"/>
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18.5"/>
   <cols>
     <col width="12.81640625" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
@@ -661,8 +661,8 @@
     <col width="29.7265625" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="12.26953125" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
     <col width="26.36328125" bestFit="1" customWidth="1" style="10" min="8" max="8"/>
-    <col width="10.90625" customWidth="1" style="2" min="9" max="24"/>
-    <col width="10.90625" customWidth="1" style="2" min="25" max="16384"/>
+    <col width="10.90625" customWidth="1" style="2" min="9" max="25"/>
+    <col width="10.90625" customWidth="1" style="2" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="37" customHeight="1">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>24946.57</v>
+        <v>22748</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3153,6 +3153,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="73">
@@ -3802,7 +3805,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>8079.17</v>
+        <v>7593.96</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3813,6 +3816,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="93">
@@ -3868,7 +3874,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>6976.86</v>
+        <v>6558.2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3879,6 +3885,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="95">
@@ -4132,7 +4141,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2675.31</v>
+        <v>2821.72</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4143,6 +4152,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="103">
@@ -4462,7 +4474,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>4065.6</v>
+        <v>3777.62</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4473,6 +4485,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="113">
@@ -4693,7 +4708,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>3990.58</v>
+        <v>3590.07</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4704,6 +4719,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="120">
@@ -4726,7 +4744,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>2094.51</v>
+        <v>1890.02</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4737,6 +4755,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H120" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="121">
@@ -4759,7 +4780,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>2204.62</v>
+        <v>2203.41</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4770,6 +4791,9 @@
         <is>
           <t>Si</t>
         </is>
+      </c>
+      <c r="H121" s="14" t="n">
+        <v>46220.40671785879</v>
       </c>
     </row>
     <row r="122">
@@ -5130,6 +5154,39 @@
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ARCOR MENTA CRISTAL/MIX 810G</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Arcor</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Golosinas</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>9750.18</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1163.webp</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
